--- a/output/pdf_financials_xlsx/MATE.xlsx
+++ b/output/pdf_financials_xlsx/MATE.xlsx
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.140619</v>
+        <v>0.195665</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.259525</v>
+        <v>0.743286</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.6132609999999999</v>
+        <v>1.372096</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.522667</v>
+        <v>1.294509</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.580854</v>
+        <v>1.233253</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.306355</v>
+        <v>0.679515</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.438454</v>
+        <v>0.998598</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.311612</v>
+        <v>0.859358</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.557819</v>
+        <v>1.469483</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>1.075089</v>
@@ -893,10 +893,10 @@
         <v>1.397057</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.599684</v>
+        <v>2.924031</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2.903195</v>
+        <v>6.979505</v>
       </c>
     </row>
     <row r="11">
@@ -916,25 +916,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.5956320000000001</v>
+        <v>-1.354467</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.495464</v>
+        <v>-1.267306</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.509427</v>
+        <v>-1.161826</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.056723</v>
+        <v>-0.429883</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.145849</v>
+        <v>-0.705993</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.047972</v>
+        <v>-0.595718</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.305624</v>
+        <v>-1.217288</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-0.866787</v>
@@ -966,43 +966,43 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003732</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004773</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00044</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010095</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006400000000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.006281</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000223</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00381</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001841</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.11585</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.010464</v>
       </c>
     </row>
     <row r="13">
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.743286</v>
+        <v>-0.739554</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.354467</v>
+        <v>-1.349694</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.267306</v>
+        <v>-1.266866</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.161826</v>
+        <v>-1.151731</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.429883</v>
+        <v>-0.429861</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.705993</v>
+        <v>-0.705353</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.566603</v>
+        <v>-0.5728839999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.158067</v>
+        <v>-1.15829</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.786544</v>
+        <v>-0.7865529999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.638888</v>
+        <v>-4.642698</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.809575</v>
+        <v>-2.811416</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.603324</v>
+        <v>-2.719174</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -1933,40 +1933,40 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.728675</v>
+        <v>-0.724943</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.285998</v>
+        <v>-1.281225</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.15509</v>
+        <v>-1.15465</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.047775</v>
+        <v>-1.03768</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.309026</v>
+        <v>-0.309004</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.571804</v>
+        <v>-0.571164</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.233397</v>
+        <v>-0.239678</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.84814</v>
+        <v>-0.848363</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.760804</v>
+        <v>-0.760813</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.711984</v>
+        <v>-4.715794</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.809575</v>
+        <v>-2.811416</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.603582</v>
+        <v>-2.719432</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -1991,34 +1991,34 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2587.625256549559</v>
+        <v>-2578.021248339973</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-730.7551180504593</v>
+        <v>-730.4767568388288</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-387.991527526282</v>
+        <v>-384.2533447385864</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-83.14369735011852</v>
+        <v>-83.13777823217471</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-118.5540569959466</v>
+        <v>-118.4213636316515</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-58.4581282638915</v>
+        <v>-60.0313083117306</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-198.3809361192522</v>
+        <v>-198.4330960795825</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-195.9249473364339</v>
+        <v>-195.9272650483887</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1081.278354395233</v>
+        <v>-1082.15265077023</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-36388.74498122005</v>
+        <v>-36412.58904287009</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         <v>2.984005</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.499852</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.057464</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.057464</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.860881</v>
       </c>
     </row>
     <row r="35">
@@ -2283,16 +2283,16 @@
         <v>2.984005</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.499852</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.057464</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.057464</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.860881</v>
       </c>
     </row>
     <row r="37">
@@ -2871,16 +2871,16 @@
         <v>0.019771</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.949686</v>
+        <v>0.449834</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.412129</v>
+        <v>0.354665</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.412129</v>
+        <v>0.354665</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.122462</v>
+        <v>0.261581</v>
       </c>
     </row>
     <row r="49">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -45202,7 +45202,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E450" s="5" t="n">
@@ -45241,13 +45241,13 @@
         </is>
       </c>
       <c r="P450" s="5" t="n">
-        <v>-1.397057</v>
+        <v>1.397057</v>
       </c>
       <c r="Q450" s="5" t="n">
-        <v>-2.924031</v>
+        <v>2.924031</v>
       </c>
       <c r="R450" s="5" t="n">
-        <v>-6.979505</v>
+        <v>6.979505</v>
       </c>
     </row>
     <row r="451">
@@ -45694,7 +45694,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -53160,7 +53160,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -54290,7 +54290,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -55296,7 +55296,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -57728,7 +57728,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">

--- a/output/pdf_financials_xlsx/MATE.xlsx
+++ b/output/pdf_financials_xlsx/MATE.xlsx
@@ -1453,12 +1453,10 @@
         <v>-1.411539</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-2.603324</v>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.928462</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-7.177641</v>
       </c>
     </row>
     <row r="21">
@@ -1498,10 +1496,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.433563</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-0.973078</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -5929,19 +5927,19 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.03559</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.061623</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.03596</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.054326</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -5953,10 +5951,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.102865</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.261304</v>
       </c>
     </row>
     <row r="111">
@@ -5969,43 +5967,43 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001712</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004011</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009879999999999999</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009464999999999999</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060585</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00386</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010528</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.308842</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001963</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004999</v>
       </c>
     </row>
     <row r="112">
@@ -6214,34 +6212,34 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.044155</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.302878</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.320985</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.08226899999999999</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07736</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.172895</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.146013</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.041357</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.078041</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -7138,43 +7136,43 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001712</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004011</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009879999999999999</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009464999999999999</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060585</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00386</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010528</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.308842</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001963</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004999</v>
       </c>
     </row>
     <row r="135">
@@ -7189,34 +7187,34 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.072516</v>
+        <v>-0.074228</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.100498</v>
+        <v>-1.104509</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.104155</v>
+        <v>-1.105143</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.042825</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.165224</v>
+        <v>-0.174689</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.601313</v>
+        <v>-0.661898</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.282918</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.922437</v>
+        <v>-0.926297</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.715185</v>
+        <v>-0.7257130000000001</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.693016</v>
+        <v>-2.001858</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -19668,7 +19666,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -20998,7 +21000,11 @@
           <t>Net proceeds from private placement 12</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -21580,7 +21586,11 @@
           <t>Acquisition of equipment 7</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27184,7 +27194,11 @@
           <t>Acquisitions of equipment 6</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -29414,7 +29428,11 @@
           <t>Acquisitions of equipment 5</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -29498,7 +29516,11 @@
           <t>Acquisitions of intangible assets 6</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -30930,7 +30952,11 @@
           <t>Accretion expense (note 13)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -31578,7 +31604,11 @@
           <t>Acquisitions of equipment</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -31652,7 +31682,11 @@
           <t>Acquisitions of intangible assets</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -33956,7 +33990,11 @@
           <t>Accretion expense (note 12)</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -43644,7 +43682,11 @@
           <t>Acquisitions of equipment (</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -43730,7 +43772,11 @@
           <t>Acquisitions of intangible assets (</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -46278,7 +46324,11 @@
           <t>Net Loss from Continuing Operations</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -49838,7 +49888,11 @@
           <t>Other Income from Discontinued Operations 5</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
